--- a/artfynd/A 55727-2022 artfynd.xlsx
+++ b/artfynd/A 55727-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55727-2022 artfynd.xlsx
+++ b/artfynd/A 55727-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,1706 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123325241</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lillingesbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>611259</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6985131</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2024_1719</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>med eventuell ulltickeporing</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123325252</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91243</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>658</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lillingesbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>611224</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6985137</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2024_1708</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123325251</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lillingesbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>611227</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6985131</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2024_1709</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123325254</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56688</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lillingesbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>611225</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6985116</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2024_1706</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Tupp</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123325250</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lillingesbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>611232</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6985138</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2024_1710</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123325243</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56680</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lillingesbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>611249</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6985155</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2024_1717</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ofir Svensson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123325244</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lillingesbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>611247</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6985152</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2024_1716</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ofir Svensson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123325240</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98386</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lillingesbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>611190</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6985143</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2024_1720</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123325246</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lillingesbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>611258</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6985139</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2024_1714</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ofir Svensson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123325247</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lillingesbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>611257</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6985139</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2024_1713</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ofir Svensson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123325248</v>
+      </c>
+      <c r="B14" t="n">
+        <v>6268</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>105336</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Peltis ferruginea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lillingesbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>611232</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6985182</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2024_1712</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Fragment</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123325249</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lillingesbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>611245</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6985142</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2024_1711</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123325245</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91243</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>658</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lillingesbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>611257</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6985146</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2024_1715</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ofir Svensson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55727-2022 artfynd.xlsx
+++ b/artfynd/A 55727-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325241</v>
+        <v>123325240</v>
       </c>
       <c r="B4" t="n">
-        <v>90952</v>
+        <v>98389</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,35 +925,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611259</v>
+        <v>611190</v>
       </c>
       <c r="R4" t="n">
-        <v>6985131</v>
+        <v>6985143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1719</t>
+          <t>2024_1720</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,12 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>med eventuell ulltickeporing</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325252</v>
+        <v>123325245</v>
       </c>
       <c r="B5" t="n">
-        <v>91243</v>
+        <v>91242</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,7 +1078,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1097,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611224</v>
+        <v>611257</v>
       </c>
       <c r="R5" t="n">
-        <v>6985137</v>
+        <v>6985146</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,7 +1122,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1708</t>
+          <t>2024_1715</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1137,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1147,7 +1142,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,7 +1162,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1178,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325251</v>
+        <v>123325250</v>
       </c>
       <c r="B6" t="n">
-        <v>90952</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,35 +1185,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1227,10 +1222,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611227</v>
+        <v>611232</v>
       </c>
       <c r="R6" t="n">
-        <v>6985131</v>
+        <v>6985138</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,7 +1252,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1709</t>
+          <t>2024_1710</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1267,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1277,7 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,10 +1303,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325254</v>
+        <v>123325251</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
+        <v>90955</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,25 +1315,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1346,16 +1341,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lillingesbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611225</v>
+        <v>611227</v>
       </c>
       <c r="R7" t="n">
-        <v>6985116</v>
+        <v>6985131</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1706</t>
+          <t>2024_1709</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1402,12 +1402,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Tupp</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1438,10 +1433,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325250</v>
+        <v>123325249</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>78769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1450,35 +1445,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1487,10 +1482,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611232</v>
+        <v>611245</v>
       </c>
       <c r="R8" t="n">
-        <v>6985138</v>
+        <v>6985142</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1517,7 +1512,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1710</t>
+          <t>2024_1711</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1527,7 +1522,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1537,7 +1532,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1568,10 +1563,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325243</v>
+        <v>123325252</v>
       </c>
       <c r="B9" t="n">
-        <v>56680</v>
+        <v>91242</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1584,21 +1579,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1606,9 +1601,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1617,10 +1612,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611249</v>
+        <v>611224</v>
       </c>
       <c r="R9" t="n">
-        <v>6985155</v>
+        <v>6985137</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1647,7 +1642,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1717</t>
+          <t>2024_1708</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1657,7 +1652,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1667,7 +1662,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1687,7 +1682,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1698,10 +1693,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325244</v>
+        <v>123325248</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>6268</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1710,35 +1705,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>105336</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1747,10 +1742,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611247</v>
+        <v>611232</v>
       </c>
       <c r="R10" t="n">
-        <v>6985152</v>
+        <v>6985182</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1777,7 +1772,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1716</t>
+          <t>2024_1712</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1787,7 +1782,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1797,7 +1792,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fragment</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1828,10 +1828,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325240</v>
+        <v>123325246</v>
       </c>
       <c r="B11" t="n">
-        <v>98386</v>
+        <v>90955</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1840,25 +1840,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611190</v>
+        <v>611258</v>
       </c>
       <c r="R11" t="n">
-        <v>6985143</v>
+        <v>6985139</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1720</t>
+          <t>2024_1714</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1958,10 +1958,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325246</v>
+        <v>123325241</v>
       </c>
       <c r="B12" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611258</v>
+        <v>611259</v>
       </c>
       <c r="R12" t="n">
-        <v>6985139</v>
+        <v>6985131</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1714</t>
+          <t>2024_1719</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2057,7 +2057,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>med eventuell ulltickeporing</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2077,7 +2082,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2091,7 +2096,7 @@
         <v>123325247</v>
       </c>
       <c r="B13" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2218,10 +2223,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325248</v>
+        <v>123325244</v>
       </c>
       <c r="B14" t="n">
-        <v>6268</v>
+        <v>98368</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2230,35 +2235,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105336</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2267,10 +2272,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611232</v>
+        <v>611247</v>
       </c>
       <c r="R14" t="n">
-        <v>6985182</v>
+        <v>6985152</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2297,7 +2302,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1712</t>
+          <t>2024_1716</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2307,7 +2312,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2317,12 +2322,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Fragment</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2353,10 +2353,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123325249</v>
+        <v>123325254</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>56691</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2365,35 +2365,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2402,10 +2397,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611245</v>
+        <v>611225</v>
       </c>
       <c r="R15" t="n">
-        <v>6985142</v>
+        <v>6985116</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2432,7 +2427,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1711</t>
+          <t>2024_1706</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2442,7 +2437,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2452,7 +2447,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2483,10 +2483,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123325245</v>
+        <v>123325243</v>
       </c>
       <c r="B16" t="n">
-        <v>91243</v>
+        <v>56683</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2499,31 +2499,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611257</v>
+        <v>611249</v>
       </c>
       <c r="R16" t="n">
-        <v>6985146</v>
+        <v>6985155</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1715</t>
+          <t>2024_1717</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2606,6 +2606,141 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123434989</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91244</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>658</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lillingesbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>611247</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6985157</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2024_1718</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ofir Svensson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 55727-2022 artfynd.xlsx
+++ b/artfynd/A 55727-2022 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325240</v>
+        <v>123325251</v>
       </c>
       <c r="B4" t="n">
-        <v>98389</v>
+        <v>90957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,25 +925,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611190</v>
+        <v>611227</v>
       </c>
       <c r="R4" t="n">
-        <v>6985143</v>
+        <v>6985131</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1720</t>
+          <t>2024_1709</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325245</v>
+        <v>123325248</v>
       </c>
       <c r="B5" t="n">
-        <v>91242</v>
+        <v>6268</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,35 +1055,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>105336</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611257</v>
+        <v>611232</v>
       </c>
       <c r="R5" t="n">
-        <v>6985146</v>
+        <v>6985182</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1715</t>
+          <t>2024_1712</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,7 +1142,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fragment</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,7 +1167,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1176,7 +1181,7 @@
         <v>123325250</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1303,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325251</v>
+        <v>123325241</v>
       </c>
       <c r="B7" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1338,12 +1343,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1352,7 +1357,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611227</v>
+        <v>611259</v>
       </c>
       <c r="R7" t="n">
         <v>6985131</v>
@@ -1382,7 +1387,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1709</t>
+          <t>2024_1719</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1392,7 +1397,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1402,7 +1407,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>med eventuell ulltickeporing</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1436,7 +1446,7 @@
         <v>123325249</v>
       </c>
       <c r="B8" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1563,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325252</v>
+        <v>123325245</v>
       </c>
       <c r="B9" t="n">
-        <v>91242</v>
+        <v>91244</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1598,7 +1608,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1612,10 +1622,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611224</v>
+        <v>611257</v>
       </c>
       <c r="R9" t="n">
-        <v>6985137</v>
+        <v>6985146</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1642,7 +1652,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1708</t>
+          <t>2024_1715</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1652,7 +1662,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1662,7 +1672,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1682,7 +1692,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1693,10 +1703,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325248</v>
+        <v>123325246</v>
       </c>
       <c r="B10" t="n">
-        <v>6268</v>
+        <v>90957</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1705,25 +1715,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105336</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1733,7 +1743,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1742,10 +1752,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611232</v>
+        <v>611258</v>
       </c>
       <c r="R10" t="n">
-        <v>6985182</v>
+        <v>6985139</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1772,7 +1782,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1712</t>
+          <t>2024_1714</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1782,7 +1792,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1792,12 +1802,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Fragment</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1817,7 +1822,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1828,10 +1833,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325246</v>
+        <v>123325247</v>
       </c>
       <c r="B11" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1863,7 +1868,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1877,7 +1882,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611258</v>
+        <v>611257</v>
       </c>
       <c r="R11" t="n">
         <v>6985139</v>
@@ -1907,7 +1912,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1714</t>
+          <t>2024_1713</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1917,7 +1922,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1927,7 +1932,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1958,10 +1963,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325241</v>
+        <v>123325252</v>
       </c>
       <c r="B12" t="n">
-        <v>90955</v>
+        <v>91244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1974,31 +1979,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2007,10 +2012,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611259</v>
+        <v>611224</v>
       </c>
       <c r="R12" t="n">
-        <v>6985131</v>
+        <v>6985137</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2037,7 +2042,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1719</t>
+          <t>2024_1708</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2047,7 +2052,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2057,12 +2062,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>med eventuell ulltickeporing</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2093,10 +2093,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325247</v>
+        <v>123325244</v>
       </c>
       <c r="B13" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2105,25 +2105,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611257</v>
+        <v>611247</v>
       </c>
       <c r="R13" t="n">
-        <v>6985139</v>
+        <v>6985152</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1713</t>
+          <t>2024_1716</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2223,10 +2223,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325244</v>
+        <v>123325254</v>
       </c>
       <c r="B14" t="n">
-        <v>98368</v>
+        <v>56691</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2235,35 +2235,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2272,10 +2267,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611247</v>
+        <v>611225</v>
       </c>
       <c r="R14" t="n">
-        <v>6985152</v>
+        <v>6985116</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2302,7 +2297,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1716</t>
+          <t>2024_1706</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2312,7 +2307,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2322,7 +2317,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2353,10 +2353,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123325254</v>
+        <v>123325240</v>
       </c>
       <c r="B15" t="n">
-        <v>56691</v>
+        <v>98391</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2391,16 +2391,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillingesbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611225</v>
+        <v>611190</v>
       </c>
       <c r="R15" t="n">
-        <v>6985116</v>
+        <v>6985143</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2427,7 +2432,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1706</t>
+          <t>2024_1720</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2437,7 +2442,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2447,12 +2452,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Tupp</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 55727-2022 artfynd.xlsx
+++ b/artfynd/A 55727-2022 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325251</v>
+        <v>123325247</v>
       </c>
       <c r="B4" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,12 +948,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611227</v>
+        <v>611257</v>
       </c>
       <c r="R4" t="n">
-        <v>6985131</v>
+        <v>6985139</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1709</t>
+          <t>2024_1713</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325248</v>
+        <v>123325244</v>
       </c>
       <c r="B5" t="n">
-        <v>6268</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,35 +1055,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105336</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611232</v>
+        <v>611247</v>
       </c>
       <c r="R5" t="n">
-        <v>6985182</v>
+        <v>6985152</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1712</t>
+          <t>2024_1716</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,12 +1142,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fragment</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,7 +1162,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1178,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325250</v>
+        <v>123325241</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>90963</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,35 +1185,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1227,10 +1222,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611232</v>
+        <v>611259</v>
       </c>
       <c r="R6" t="n">
-        <v>6985138</v>
+        <v>6985131</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,7 +1252,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1710</t>
+          <t>2024_1719</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1267,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1277,7 +1272,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>med eventuell ulltickeporing</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325241</v>
+        <v>123325240</v>
       </c>
       <c r="B7" t="n">
-        <v>90957</v>
+        <v>98397</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,35 +1320,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611259</v>
+        <v>611190</v>
       </c>
       <c r="R7" t="n">
-        <v>6985131</v>
+        <v>6985143</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1719</t>
+          <t>2024_1720</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1407,12 +1407,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>med eventuell ulltickeporing</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,10 +1438,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325249</v>
+        <v>123325251</v>
       </c>
       <c r="B8" t="n">
-        <v>78771</v>
+        <v>90963</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1459,31 +1454,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1492,10 +1487,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611245</v>
+        <v>611227</v>
       </c>
       <c r="R8" t="n">
-        <v>6985142</v>
+        <v>6985131</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1522,7 +1517,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1711</t>
+          <t>2024_1709</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1532,7 +1527,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1542,7 +1537,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1573,10 +1568,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325245</v>
+        <v>123325250</v>
       </c>
       <c r="B9" t="n">
-        <v>91244</v>
+        <v>98376</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1585,35 +1580,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1622,10 +1617,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611257</v>
+        <v>611232</v>
       </c>
       <c r="R9" t="n">
-        <v>6985146</v>
+        <v>6985138</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1652,7 +1647,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1715</t>
+          <t>2024_1710</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1662,7 +1657,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1672,7 +1667,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1692,7 +1687,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1703,10 +1698,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325246</v>
+        <v>123325249</v>
       </c>
       <c r="B10" t="n">
-        <v>90957</v>
+        <v>78772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1719,31 +1714,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1752,10 +1747,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611258</v>
+        <v>611245</v>
       </c>
       <c r="R10" t="n">
-        <v>6985139</v>
+        <v>6985142</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1782,7 +1777,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1714</t>
+          <t>2024_1711</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1792,7 +1787,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1802,7 +1797,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1822,7 +1817,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1833,10 +1828,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325247</v>
+        <v>123325248</v>
       </c>
       <c r="B11" t="n">
-        <v>90957</v>
+        <v>6268</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1845,35 +1840,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>105336</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611257</v>
+        <v>611232</v>
       </c>
       <c r="R11" t="n">
-        <v>6985139</v>
+        <v>6985182</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1912,7 +1907,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1713</t>
+          <t>2024_1712</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1933,6 +1928,11 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>08:25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fragment</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1963,10 +1963,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325252</v>
+        <v>123325245</v>
       </c>
       <c r="B12" t="n">
-        <v>91244</v>
+        <v>91250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611224</v>
+        <v>611257</v>
       </c>
       <c r="R12" t="n">
-        <v>6985137</v>
+        <v>6985146</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1708</t>
+          <t>2024_1715</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2093,10 +2093,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325244</v>
+        <v>123325243</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>56683</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2105,35 +2105,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611247</v>
+        <v>611249</v>
       </c>
       <c r="R13" t="n">
-        <v>6985152</v>
+        <v>6985155</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1716</t>
+          <t>2024_1717</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2223,10 +2223,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325254</v>
+        <v>123325252</v>
       </c>
       <c r="B14" t="n">
-        <v>56691</v>
+        <v>91250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2235,25 +2235,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2261,16 +2261,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lillingesbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611225</v>
+        <v>611224</v>
       </c>
       <c r="R14" t="n">
-        <v>6985116</v>
+        <v>6985137</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2297,7 +2302,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1706</t>
+          <t>2024_1708</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2307,7 +2312,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2317,12 +2322,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Tupp</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2353,10 +2353,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123325240</v>
+        <v>123325254</v>
       </c>
       <c r="B15" t="n">
-        <v>98391</v>
+        <v>56691</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2391,21 +2391,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillingesbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611190</v>
+        <v>611225</v>
       </c>
       <c r="R15" t="n">
-        <v>6985143</v>
+        <v>6985116</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2432,7 +2427,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1720</t>
+          <t>2024_1706</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2442,7 +2437,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2452,7 +2447,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2483,10 +2483,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123325243</v>
+        <v>123325246</v>
       </c>
       <c r="B16" t="n">
-        <v>56683</v>
+        <v>90963</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2499,21 +2499,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2521,9 +2521,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611249</v>
+        <v>611258</v>
       </c>
       <c r="R16" t="n">
-        <v>6985155</v>
+        <v>6985139</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1717</t>
+          <t>2024_1714</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2616,7 +2616,7 @@
         <v>123434989</v>
       </c>
       <c r="B17" t="n">
-        <v>91244</v>
+        <v>91250</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 55727-2022 artfynd.xlsx
+++ b/artfynd/A 55727-2022 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325246</v>
+        <v>123325245</v>
       </c>
       <c r="B4" t="n">
-        <v>90966</v>
+        <v>91270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,26 +929,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611258</v>
+        <v>611257</v>
       </c>
       <c r="R4" t="n">
-        <v>6985139</v>
+        <v>6985146</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1714</t>
+          <t>2024_1715</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325250</v>
+        <v>123325249</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,35 +1055,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611232</v>
+        <v>611245</v>
       </c>
       <c r="R5" t="n">
-        <v>6985138</v>
+        <v>6985142</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1710</t>
+          <t>2024_1711</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325247</v>
+        <v>123325252</v>
       </c>
       <c r="B6" t="n">
-        <v>90966</v>
+        <v>91270</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,26 +1189,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1222,10 +1222,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611257</v>
+        <v>611224</v>
       </c>
       <c r="R6" t="n">
-        <v>6985139</v>
+        <v>6985137</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1713</t>
+          <t>2024_1708</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1303,10 +1303,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325248</v>
+        <v>123325251</v>
       </c>
       <c r="B7" t="n">
-        <v>6268</v>
+        <v>90983</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,25 +1315,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105336</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611232</v>
+        <v>611227</v>
       </c>
       <c r="R7" t="n">
-        <v>6985182</v>
+        <v>6985131</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1712</t>
+          <t>2024_1709</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1402,12 +1402,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Fragment</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1441,7 +1436,7 @@
         <v>123325240</v>
       </c>
       <c r="B8" t="n">
-        <v>98400</v>
+        <v>98417</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1568,10 +1563,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325249</v>
+        <v>123325243</v>
       </c>
       <c r="B9" t="n">
-        <v>78775</v>
+        <v>56689</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1584,31 +1579,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1617,10 +1612,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611245</v>
+        <v>611249</v>
       </c>
       <c r="R9" t="n">
-        <v>6985142</v>
+        <v>6985155</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1647,7 +1642,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1711</t>
+          <t>2024_1717</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1657,7 +1652,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1667,7 +1662,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1687,7 +1682,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1698,10 +1693,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325243</v>
+        <v>123325248</v>
       </c>
       <c r="B10" t="n">
-        <v>56683</v>
+        <v>6269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1710,20 +1705,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>105336</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1736,9 +1731,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1747,10 +1742,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611249</v>
+        <v>611232</v>
       </c>
       <c r="R10" t="n">
-        <v>6985155</v>
+        <v>6985182</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1777,7 +1772,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1717</t>
+          <t>2024_1712</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1787,7 +1782,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1797,7 +1792,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fragment</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1828,10 +1828,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325251</v>
+        <v>123325244</v>
       </c>
       <c r="B11" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1840,35 +1840,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611227</v>
+        <v>611247</v>
       </c>
       <c r="R11" t="n">
-        <v>6985131</v>
+        <v>6985152</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1709</t>
+          <t>2024_1716</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1958,10 +1958,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325254</v>
+        <v>123325247</v>
       </c>
       <c r="B12" t="n">
-        <v>56691</v>
+        <v>90983</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1970,30 +1970,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2002,10 +2007,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611225</v>
+        <v>611257</v>
       </c>
       <c r="R12" t="n">
-        <v>6985116</v>
+        <v>6985139</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2032,7 +2037,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1706</t>
+          <t>2024_1713</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2042,7 +2047,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2052,12 +2057,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Tupp</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2091,7 +2091,7 @@
         <v>123325241</v>
       </c>
       <c r="B13" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325245</v>
+        <v>123325254</v>
       </c>
       <c r="B14" t="n">
-        <v>91253</v>
+        <v>56697</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2235,35 +2235,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2272,10 +2267,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611257</v>
+        <v>611225</v>
       </c>
       <c r="R14" t="n">
-        <v>6985146</v>
+        <v>6985116</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2302,7 +2297,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1715</t>
+          <t>2024_1706</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2312,7 +2307,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2322,7 +2317,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2353,10 +2353,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123325244</v>
+        <v>123325250</v>
       </c>
       <c r="B15" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611247</v>
+        <v>611232</v>
       </c>
       <c r="R15" t="n">
-        <v>6985152</v>
+        <v>6985138</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1716</t>
+          <t>2024_1710</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2483,10 +2483,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123325252</v>
+        <v>123325246</v>
       </c>
       <c r="B16" t="n">
-        <v>91253</v>
+        <v>90983</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2499,21 +2499,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611224</v>
+        <v>611258</v>
       </c>
       <c r="R16" t="n">
-        <v>6985137</v>
+        <v>6985139</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1708</t>
+          <t>2024_1714</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2616,7 +2616,7 @@
         <v>123434989</v>
       </c>
       <c r="B17" t="n">
-        <v>91253</v>
+        <v>91270</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 55727-2022 artfynd.xlsx
+++ b/artfynd/A 55727-2022 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325245</v>
+        <v>123325246</v>
       </c>
       <c r="B4" t="n">
-        <v>91270</v>
+        <v>90988</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,26 +929,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611257</v>
+        <v>611258</v>
       </c>
       <c r="R4" t="n">
-        <v>6985146</v>
+        <v>6985139</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1715</t>
+          <t>2024_1714</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,7 +1046,7 @@
         <v>123325249</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325252</v>
+        <v>123325247</v>
       </c>
       <c r="B6" t="n">
-        <v>91270</v>
+        <v>90988</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,26 +1189,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1222,10 +1222,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611224</v>
+        <v>611257</v>
       </c>
       <c r="R6" t="n">
-        <v>6985137</v>
+        <v>6985139</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1708</t>
+          <t>2024_1713</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1306,7 +1306,7 @@
         <v>123325251</v>
       </c>
       <c r="B7" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325240</v>
+        <v>123325245</v>
       </c>
       <c r="B8" t="n">
-        <v>98417</v>
+        <v>91275</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1445,35 +1445,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611190</v>
+        <v>611257</v>
       </c>
       <c r="R8" t="n">
-        <v>6985143</v>
+        <v>6985146</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1720</t>
+          <t>2024_1715</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1566,7 +1566,7 @@
         <v>123325243</v>
       </c>
       <c r="B9" t="n">
-        <v>56689</v>
+        <v>56692</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1693,10 +1693,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325248</v>
+        <v>123325254</v>
       </c>
       <c r="B10" t="n">
-        <v>6269</v>
+        <v>56700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105336</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1731,21 +1731,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillingesbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611232</v>
+        <v>611225</v>
       </c>
       <c r="R10" t="n">
-        <v>6985182</v>
+        <v>6985116</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1772,7 +1767,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1712</t>
+          <t>2024_1706</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1782,7 +1777,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1792,12 +1787,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fragment</t>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1828,10 +1823,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325244</v>
+        <v>123325250</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1863,7 +1858,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1877,10 +1872,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611247</v>
+        <v>611232</v>
       </c>
       <c r="R11" t="n">
-        <v>6985152</v>
+        <v>6985138</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1907,7 +1902,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1716</t>
+          <t>2024_1710</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1917,7 +1912,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1927,7 +1922,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1947,7 +1942,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1958,10 +1953,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325247</v>
+        <v>123325241</v>
       </c>
       <c r="B12" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1993,12 +1988,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2007,10 +2002,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611257</v>
+        <v>611259</v>
       </c>
       <c r="R12" t="n">
-        <v>6985139</v>
+        <v>6985131</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2037,7 +2032,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1713</t>
+          <t>2024_1719</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2047,7 +2042,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2057,7 +2052,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>med eventuell ulltickeporing</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2088,10 +2088,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325241</v>
+        <v>123325240</v>
       </c>
       <c r="B13" t="n">
-        <v>90983</v>
+        <v>98523</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2100,35 +2100,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611259</v>
+        <v>611190</v>
       </c>
       <c r="R13" t="n">
-        <v>6985131</v>
+        <v>6985143</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1719</t>
+          <t>2024_1720</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2187,12 +2187,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>med eventuell ulltickeporing</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2223,10 +2218,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325254</v>
+        <v>123325244</v>
       </c>
       <c r="B14" t="n">
-        <v>56697</v>
+        <v>98502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2235,30 +2230,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611225</v>
+        <v>611247</v>
       </c>
       <c r="R14" t="n">
-        <v>6985116</v>
+        <v>6985152</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1706</t>
+          <t>2024_1716</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2317,12 +2317,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Tupp</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2342,7 +2337,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2353,10 +2348,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123325250</v>
+        <v>123325248</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>6271</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2365,35 +2360,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>105336</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2405,7 +2400,7 @@
         <v>611232</v>
       </c>
       <c r="R15" t="n">
-        <v>6985138</v>
+        <v>6985182</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2432,7 +2427,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1710</t>
+          <t>2024_1712</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2442,7 +2437,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2452,7 +2447,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Fragment</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2483,10 +2483,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123325246</v>
+        <v>123325252</v>
       </c>
       <c r="B16" t="n">
-        <v>90983</v>
+        <v>91275</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2499,21 +2499,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611258</v>
+        <v>611224</v>
       </c>
       <c r="R16" t="n">
-        <v>6985139</v>
+        <v>6985137</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1714</t>
+          <t>2024_1708</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2616,7 +2616,7 @@
         <v>123434989</v>
       </c>
       <c r="B17" t="n">
-        <v>91270</v>
+        <v>91275</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 55727-2022 artfynd.xlsx
+++ b/artfynd/A 55727-2022 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325246</v>
+        <v>123325252</v>
       </c>
       <c r="B4" t="n">
-        <v>90988</v>
+        <v>91277</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611258</v>
+        <v>611224</v>
       </c>
       <c r="R4" t="n">
-        <v>6985139</v>
+        <v>6985137</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1714</t>
+          <t>2024_1708</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325249</v>
+        <v>123325251</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,31 +1059,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611245</v>
+        <v>611227</v>
       </c>
       <c r="R5" t="n">
-        <v>6985142</v>
+        <v>6985131</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1711</t>
+          <t>2024_1709</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325247</v>
+        <v>123325248</v>
       </c>
       <c r="B6" t="n">
-        <v>90988</v>
+        <v>6271</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,35 +1185,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>105336</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1222,10 +1222,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611257</v>
+        <v>611232</v>
       </c>
       <c r="R6" t="n">
-        <v>6985139</v>
+        <v>6985182</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1713</t>
+          <t>2024_1712</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1273,6 +1273,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>08:25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fragment</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,7 +1297,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1303,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325251</v>
+        <v>123325244</v>
       </c>
       <c r="B7" t="n">
-        <v>90988</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,35 +1320,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611227</v>
+        <v>611247</v>
       </c>
       <c r="R7" t="n">
-        <v>6985131</v>
+        <v>6985152</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,7 +1387,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1709</t>
+          <t>2024_1716</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1392,7 +1397,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1402,7 +1407,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,7 +1427,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1436,7 +1441,7 @@
         <v>123325245</v>
       </c>
       <c r="B8" t="n">
-        <v>91275</v>
+        <v>91277</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1563,10 +1568,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325243</v>
+        <v>123325249</v>
       </c>
       <c r="B9" t="n">
-        <v>56692</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1579,31 +1584,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1612,10 +1617,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611249</v>
+        <v>611245</v>
       </c>
       <c r="R9" t="n">
-        <v>6985155</v>
+        <v>6985142</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1642,7 +1647,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1717</t>
+          <t>2024_1711</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1652,7 +1657,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1662,7 +1667,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1682,7 +1687,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1693,10 +1698,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325254</v>
+        <v>123325247</v>
       </c>
       <c r="B10" t="n">
-        <v>56700</v>
+        <v>90990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1705,30 +1710,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1737,10 +1747,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611225</v>
+        <v>611257</v>
       </c>
       <c r="R10" t="n">
-        <v>6985116</v>
+        <v>6985139</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1767,7 +1777,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1706</t>
+          <t>2024_1713</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1777,7 +1787,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1787,12 +1797,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tupp</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1812,7 +1817,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1826,7 +1831,7 @@
         <v>123325250</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1956,7 +1961,7 @@
         <v>123325241</v>
       </c>
       <c r="B12" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2088,10 +2093,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325240</v>
+        <v>123325243</v>
       </c>
       <c r="B13" t="n">
-        <v>98523</v>
+        <v>56692</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2100,25 +2105,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2126,9 +2131,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2137,10 +2142,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611190</v>
+        <v>611249</v>
       </c>
       <c r="R13" t="n">
-        <v>6985143</v>
+        <v>6985155</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2167,7 +2172,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1720</t>
+          <t>2024_1717</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2177,7 +2182,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2187,7 +2192,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2207,7 +2212,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2218,10 +2223,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325244</v>
+        <v>123325240</v>
       </c>
       <c r="B14" t="n">
-        <v>98502</v>
+        <v>98525</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2230,30 +2235,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2267,10 +2272,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611247</v>
+        <v>611190</v>
       </c>
       <c r="R14" t="n">
-        <v>6985152</v>
+        <v>6985143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2297,7 +2302,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1716</t>
+          <t>2024_1720</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2307,7 +2312,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2317,7 +2322,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2337,7 +2342,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2348,10 +2353,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123325248</v>
+        <v>123325254</v>
       </c>
       <c r="B15" t="n">
-        <v>6271</v>
+        <v>56700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2364,21 +2369,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105336</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2386,21 +2391,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillingesbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611232</v>
+        <v>611225</v>
       </c>
       <c r="R15" t="n">
-        <v>6985182</v>
+        <v>6985116</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1712</t>
+          <t>2024_1706</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Fragment</t>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2483,10 +2483,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123325252</v>
+        <v>123325246</v>
       </c>
       <c r="B16" t="n">
-        <v>91275</v>
+        <v>90990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2499,21 +2499,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611224</v>
+        <v>611258</v>
       </c>
       <c r="R16" t="n">
-        <v>6985137</v>
+        <v>6985139</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1708</t>
+          <t>2024_1714</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2616,7 +2616,7 @@
         <v>123434989</v>
       </c>
       <c r="B17" t="n">
-        <v>91275</v>
+        <v>91277</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 55727-2022 artfynd.xlsx
+++ b/artfynd/A 55727-2022 artfynd.xlsx
@@ -1568,10 +1568,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325249</v>
+        <v>123325247</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1584,31 +1584,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611245</v>
+        <v>611257</v>
       </c>
       <c r="R9" t="n">
-        <v>6985142</v>
+        <v>6985139</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1711</t>
+          <t>2024_1713</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1698,10 +1698,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325247</v>
+        <v>123325249</v>
       </c>
       <c r="B10" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1714,31 +1714,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611257</v>
+        <v>611245</v>
       </c>
       <c r="R10" t="n">
-        <v>6985139</v>
+        <v>6985142</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1713</t>
+          <t>2024_1711</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">

--- a/artfynd/A 55727-2022 artfynd.xlsx
+++ b/artfynd/A 55727-2022 artfynd.xlsx
@@ -1568,10 +1568,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325247</v>
+        <v>123325250</v>
       </c>
       <c r="B9" t="n">
-        <v>90990</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1580,35 +1580,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611257</v>
+        <v>611232</v>
       </c>
       <c r="R9" t="n">
-        <v>6985139</v>
+        <v>6985138</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1713</t>
+          <t>2024_1710</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1828,10 +1828,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325250</v>
+        <v>123325247</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1840,35 +1840,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611232</v>
+        <v>611257</v>
       </c>
       <c r="R11" t="n">
-        <v>6985138</v>
+        <v>6985139</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1710</t>
+          <t>2024_1713</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 55727-2022 artfynd.xlsx
+++ b/artfynd/A 55727-2022 artfynd.xlsx
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325251</v>
+        <v>123325245</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>91277</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,31 +1059,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611227</v>
+        <v>611257</v>
       </c>
       <c r="R5" t="n">
-        <v>6985131</v>
+        <v>6985146</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1709</t>
+          <t>2024_1715</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1173,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325248</v>
+        <v>123325251</v>
       </c>
       <c r="B6" t="n">
-        <v>6271</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,25 +1185,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105336</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1222,10 +1222,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611232</v>
+        <v>611227</v>
       </c>
       <c r="R6" t="n">
-        <v>6985182</v>
+        <v>6985131</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1712</t>
+          <t>2024_1709</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,12 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fragment</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,10 +1303,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325244</v>
+        <v>123325247</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,25 +1315,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1348,7 +1343,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611247</v>
+        <v>611257</v>
       </c>
       <c r="R7" t="n">
-        <v>6985152</v>
+        <v>6985139</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1387,7 +1382,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1716</t>
+          <t>2024_1713</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1397,7 +1392,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1407,7 +1402,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1438,10 +1433,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325245</v>
+        <v>123325248</v>
       </c>
       <c r="B8" t="n">
-        <v>91277</v>
+        <v>6271</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1450,35 +1445,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>105336</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1487,10 +1482,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611257</v>
+        <v>611232</v>
       </c>
       <c r="R8" t="n">
-        <v>6985146</v>
+        <v>6985182</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1517,7 +1512,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1715</t>
+          <t>2024_1712</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1527,7 +1522,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1537,7 +1532,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fragment</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1568,10 +1568,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325250</v>
+        <v>123325243</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>56692</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1580,35 +1580,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611232</v>
+        <v>611249</v>
       </c>
       <c r="R9" t="n">
-        <v>6985138</v>
+        <v>6985155</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1710</t>
+          <t>2024_1717</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1698,10 +1698,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325249</v>
+        <v>123325254</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1710,35 +1710,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1747,10 +1742,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611245</v>
+        <v>611225</v>
       </c>
       <c r="R10" t="n">
-        <v>6985142</v>
+        <v>6985116</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1777,7 +1772,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1711</t>
+          <t>2024_1706</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1787,7 +1782,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1797,7 +1792,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1828,7 +1828,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325247</v>
+        <v>123325241</v>
       </c>
       <c r="B11" t="n">
         <v>90990</v>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611257</v>
+        <v>611259</v>
       </c>
       <c r="R11" t="n">
-        <v>6985139</v>
+        <v>6985131</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1713</t>
+          <t>2024_1719</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1927,7 +1927,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>med eventuell ulltickeporing</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1947,7 +1952,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1958,10 +1963,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325241</v>
+        <v>123325249</v>
       </c>
       <c r="B12" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1974,31 +1979,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2007,10 +2012,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611259</v>
+        <v>611245</v>
       </c>
       <c r="R12" t="n">
-        <v>6985131</v>
+        <v>6985142</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2037,7 +2042,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1719</t>
+          <t>2024_1711</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2047,7 +2052,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2057,12 +2062,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>med eventuell ulltickeporing</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2093,10 +2093,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325243</v>
+        <v>123325246</v>
       </c>
       <c r="B13" t="n">
-        <v>56692</v>
+        <v>90990</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2109,21 +2109,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2131,9 +2131,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611249</v>
+        <v>611258</v>
       </c>
       <c r="R13" t="n">
-        <v>6985155</v>
+        <v>6985139</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1717</t>
+          <t>2024_1714</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2223,10 +2223,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325240</v>
+        <v>123325244</v>
       </c>
       <c r="B14" t="n">
-        <v>98525</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2235,30 +2235,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611190</v>
+        <v>611247</v>
       </c>
       <c r="R14" t="n">
-        <v>6985143</v>
+        <v>6985152</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1720</t>
+          <t>2024_1716</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2353,10 +2353,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123325254</v>
+        <v>123325250</v>
       </c>
       <c r="B15" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2365,30 +2365,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2397,10 +2402,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611225</v>
+        <v>611232</v>
       </c>
       <c r="R15" t="n">
-        <v>6985116</v>
+        <v>6985138</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2427,7 +2432,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1706</t>
+          <t>2024_1710</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2437,7 +2442,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2447,12 +2452,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Tupp</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2483,10 +2483,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123325246</v>
+        <v>123325240</v>
       </c>
       <c r="B16" t="n">
-        <v>90990</v>
+        <v>98100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2495,25 +2495,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611258</v>
+        <v>611190</v>
       </c>
       <c r="R16" t="n">
-        <v>6985139</v>
+        <v>6985143</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1714</t>
+          <t>2024_1720</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">

--- a/artfynd/A 55727-2022 artfynd.xlsx
+++ b/artfynd/A 55727-2022 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325252</v>
+        <v>123325248</v>
       </c>
       <c r="B4" t="n">
-        <v>91277</v>
+        <v>6271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,25 +925,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>105336</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611224</v>
+        <v>611232</v>
       </c>
       <c r="R4" t="n">
-        <v>6985137</v>
+        <v>6985182</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1708</t>
+          <t>2024_1712</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1012,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fragment</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325245</v>
+        <v>123325246</v>
       </c>
       <c r="B5" t="n">
-        <v>91277</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,26 +1064,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1092,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611257</v>
+        <v>611258</v>
       </c>
       <c r="R5" t="n">
-        <v>6985146</v>
+        <v>6985139</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1127,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1715</t>
+          <t>2024_1714</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1132,7 +1137,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,7 +1147,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325251</v>
+        <v>123325249</v>
       </c>
       <c r="B6" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,31 +1194,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1222,10 +1227,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611227</v>
+        <v>611245</v>
       </c>
       <c r="R6" t="n">
-        <v>6985131</v>
+        <v>6985142</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1252,7 +1257,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1709</t>
+          <t>2024_1711</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1262,7 +1267,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1277,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1303,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325247</v>
+        <v>123325254</v>
       </c>
       <c r="B7" t="n">
-        <v>90990</v>
+        <v>56700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,35 +1320,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611257</v>
+        <v>611225</v>
       </c>
       <c r="R7" t="n">
-        <v>6985139</v>
+        <v>6985116</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1713</t>
+          <t>2024_1706</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1402,7 +1402,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,7 +1427,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1433,10 +1438,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325248</v>
+        <v>123325250</v>
       </c>
       <c r="B8" t="n">
-        <v>6271</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1445,35 +1450,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105336</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1485,7 +1490,7 @@
         <v>611232</v>
       </c>
       <c r="R8" t="n">
-        <v>6985182</v>
+        <v>6985138</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1512,7 +1517,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1712</t>
+          <t>2024_1710</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1522,7 +1527,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1532,12 +1537,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fragment</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1568,10 +1568,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325243</v>
+        <v>123325241</v>
       </c>
       <c r="B9" t="n">
-        <v>56692</v>
+        <v>90990</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1584,31 +1584,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611249</v>
+        <v>611259</v>
       </c>
       <c r="R9" t="n">
-        <v>6985155</v>
+        <v>6985131</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1717</t>
+          <t>2024_1719</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1667,7 +1667,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>med eventuell ulltickeporing</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1687,7 +1692,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1698,10 +1703,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325254</v>
+        <v>123325243</v>
       </c>
       <c r="B10" t="n">
-        <v>56700</v>
+        <v>56692</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1710,25 +1715,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1736,16 +1741,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillingesbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611225</v>
+        <v>611249</v>
       </c>
       <c r="R10" t="n">
-        <v>6985116</v>
+        <v>6985155</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1772,7 +1782,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1706</t>
+          <t>2024_1717</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1782,7 +1792,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1792,12 +1802,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tupp</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1817,7 +1822,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1828,7 +1833,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325241</v>
+        <v>123325247</v>
       </c>
       <c r="B11" t="n">
         <v>90990</v>
@@ -1863,12 +1868,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1877,10 +1882,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611259</v>
+        <v>611257</v>
       </c>
       <c r="R11" t="n">
-        <v>6985131</v>
+        <v>6985139</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1907,7 +1912,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1719</t>
+          <t>2024_1713</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1917,7 +1922,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1927,12 +1932,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>med eventuell ulltickeporing</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1963,10 +1963,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325249</v>
+        <v>123325251</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1979,31 +1979,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611245</v>
+        <v>611227</v>
       </c>
       <c r="R12" t="n">
-        <v>6985142</v>
+        <v>6985131</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1711</t>
+          <t>2024_1709</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2093,10 +2093,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325246</v>
+        <v>123325252</v>
       </c>
       <c r="B13" t="n">
-        <v>90990</v>
+        <v>91277</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2109,21 +2109,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611258</v>
+        <v>611224</v>
       </c>
       <c r="R13" t="n">
-        <v>6985139</v>
+        <v>6985137</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1714</t>
+          <t>2024_1708</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2223,10 +2223,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325244</v>
+        <v>123325245</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>91277</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2235,25 +2235,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611247</v>
+        <v>611257</v>
       </c>
       <c r="R14" t="n">
-        <v>6985152</v>
+        <v>6985146</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1716</t>
+          <t>2024_1715</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2353,7 +2353,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123325250</v>
+        <v>123325244</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611232</v>
+        <v>611247</v>
       </c>
       <c r="R15" t="n">
-        <v>6985138</v>
+        <v>6985152</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1710</t>
+          <t>2024_1716</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 55727-2022 artfynd.xlsx
+++ b/artfynd/A 55727-2022 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325248</v>
+        <v>123325250</v>
       </c>
       <c r="B4" t="n">
-        <v>6271</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,35 +925,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105336</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -965,7 +965,7 @@
         <v>611232</v>
       </c>
       <c r="R4" t="n">
-        <v>6985182</v>
+        <v>6985138</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1712</t>
+          <t>2024_1710</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,12 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fragment</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,7 +1043,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325246</v>
+        <v>123325247</v>
       </c>
       <c r="B5" t="n">
         <v>90990</v>
@@ -1083,7 +1078,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1097,7 +1092,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611258</v>
+        <v>611257</v>
       </c>
       <c r="R5" t="n">
         <v>6985139</v>
@@ -1127,7 +1122,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1714</t>
+          <t>2024_1713</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1137,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1147,7 +1142,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325249</v>
+        <v>123325244</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,35 +1185,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1227,10 +1222,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611245</v>
+        <v>611247</v>
       </c>
       <c r="R6" t="n">
-        <v>6985142</v>
+        <v>6985152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,7 +1252,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1711</t>
+          <t>2024_1716</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1267,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1277,7 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,7 +1292,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1308,10 +1303,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325254</v>
+        <v>123325252</v>
       </c>
       <c r="B7" t="n">
-        <v>56700</v>
+        <v>91277</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,25 +1315,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1346,16 +1341,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lillingesbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611225</v>
+        <v>611224</v>
       </c>
       <c r="R7" t="n">
-        <v>6985116</v>
+        <v>6985137</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1706</t>
+          <t>2024_1708</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1402,12 +1402,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Tupp</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1438,10 +1433,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325250</v>
+        <v>123325243</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1450,35 +1445,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1487,10 +1482,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611232</v>
+        <v>611249</v>
       </c>
       <c r="R8" t="n">
-        <v>6985138</v>
+        <v>6985155</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1517,7 +1512,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1710</t>
+          <t>2024_1717</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1527,7 +1522,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1537,7 +1532,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1557,7 +1552,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1568,10 +1563,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325241</v>
+        <v>123325240</v>
       </c>
       <c r="B9" t="n">
-        <v>90990</v>
+        <v>98100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1580,35 +1575,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1617,10 +1612,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611259</v>
+        <v>611190</v>
       </c>
       <c r="R9" t="n">
-        <v>6985131</v>
+        <v>6985143</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1647,7 +1642,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1719</t>
+          <t>2024_1720</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1657,7 +1652,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1667,12 +1662,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>med eventuell ulltickeporing</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1703,10 +1693,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325243</v>
+        <v>123325254</v>
       </c>
       <c r="B10" t="n">
-        <v>56692</v>
+        <v>56700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1715,25 +1705,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1741,21 +1731,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillingesbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611249</v>
+        <v>611225</v>
       </c>
       <c r="R10" t="n">
-        <v>6985155</v>
+        <v>6985116</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1782,7 +1767,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1717</t>
+          <t>2024_1706</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1792,7 +1777,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1802,7 +1787,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1822,7 +1812,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1833,10 +1823,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123325247</v>
+        <v>123325245</v>
       </c>
       <c r="B11" t="n">
-        <v>90990</v>
+        <v>91277</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1849,21 +1839,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1885,7 +1875,7 @@
         <v>611257</v>
       </c>
       <c r="R11" t="n">
-        <v>6985139</v>
+        <v>6985146</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1912,7 +1902,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1713</t>
+          <t>2024_1715</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1922,7 +1912,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1932,7 +1922,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1963,10 +1953,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325251</v>
+        <v>123325249</v>
       </c>
       <c r="B12" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1979,31 +1969,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2012,10 +2002,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611227</v>
+        <v>611245</v>
       </c>
       <c r="R12" t="n">
-        <v>6985131</v>
+        <v>6985142</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2042,7 +2032,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1709</t>
+          <t>2024_1711</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2052,7 +2042,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2062,7 +2052,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2093,10 +2083,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325252</v>
+        <v>123325246</v>
       </c>
       <c r="B13" t="n">
-        <v>91277</v>
+        <v>90990</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2109,21 +2099,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2142,10 +2132,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611224</v>
+        <v>611258</v>
       </c>
       <c r="R13" t="n">
-        <v>6985137</v>
+        <v>6985139</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2172,7 +2162,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1708</t>
+          <t>2024_1714</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2182,7 +2172,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2192,7 +2182,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2212,7 +2202,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2223,10 +2213,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325245</v>
+        <v>123325248</v>
       </c>
       <c r="B14" t="n">
-        <v>91277</v>
+        <v>6271</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2235,35 +2225,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>105336</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2272,10 +2262,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611257</v>
+        <v>611232</v>
       </c>
       <c r="R14" t="n">
-        <v>6985146</v>
+        <v>6985182</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2302,7 +2292,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1715</t>
+          <t>2024_1712</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2312,7 +2302,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2322,7 +2312,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Fragment</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2342,7 +2337,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2353,10 +2348,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123325244</v>
+        <v>123325241</v>
       </c>
       <c r="B15" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2365,35 +2360,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2402,10 +2397,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611247</v>
+        <v>611259</v>
       </c>
       <c r="R15" t="n">
-        <v>6985152</v>
+        <v>6985131</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2432,7 +2427,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1716</t>
+          <t>2024_1719</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2442,7 +2437,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2452,7 +2447,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>med eventuell ulltickeporing</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2483,10 +2483,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123325240</v>
+        <v>123325251</v>
       </c>
       <c r="B16" t="n">
-        <v>98100</v>
+        <v>90990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2495,25 +2495,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611190</v>
+        <v>611227</v>
       </c>
       <c r="R16" t="n">
-        <v>6985143</v>
+        <v>6985131</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1720</t>
+          <t>2024_1709</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 55727-2022 artfynd.xlsx
+++ b/artfynd/A 55727-2022 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325250</v>
+        <v>123325241</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,35 +925,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611232</v>
+        <v>611259</v>
       </c>
       <c r="R4" t="n">
-        <v>6985138</v>
+        <v>6985131</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1710</t>
+          <t>2024_1719</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1012,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>med eventuell ulltickeporing</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325247</v>
+        <v>123325254</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,35 +1060,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611257</v>
+        <v>611225</v>
       </c>
       <c r="R5" t="n">
-        <v>6985139</v>
+        <v>6985116</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1713</t>
+          <t>2024_1706</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,7 +1142,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,7 +1167,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1173,7 +1178,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325244</v>
+        <v>123325250</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1222,10 +1227,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611247</v>
+        <v>611232</v>
       </c>
       <c r="R6" t="n">
-        <v>6985152</v>
+        <v>6985138</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1252,7 +1257,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1716</t>
+          <t>2024_1710</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1262,7 +1267,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1277,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,7 +1297,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1303,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325252</v>
+        <v>123325251</v>
       </c>
       <c r="B7" t="n">
-        <v>91277</v>
+        <v>90990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1319,21 +1324,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1343,7 +1348,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611224</v>
+        <v>611227</v>
       </c>
       <c r="R7" t="n">
-        <v>6985137</v>
+        <v>6985131</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,7 +1387,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1708</t>
+          <t>2024_1709</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1392,7 +1397,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1402,7 +1407,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1433,10 +1438,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325243</v>
+        <v>123325248</v>
       </c>
       <c r="B8" t="n">
-        <v>56692</v>
+        <v>6271</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1445,20 +1450,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>105336</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1471,9 +1476,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1482,10 +1487,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611249</v>
+        <v>611232</v>
       </c>
       <c r="R8" t="n">
-        <v>6985155</v>
+        <v>6985182</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1512,7 +1517,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1717</t>
+          <t>2024_1712</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1522,7 +1527,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1532,7 +1537,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fragment</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1552,7 +1562,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1563,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325240</v>
+        <v>123325244</v>
       </c>
       <c r="B9" t="n">
-        <v>98100</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1575,30 +1585,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1612,10 +1622,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611190</v>
+        <v>611247</v>
       </c>
       <c r="R9" t="n">
-        <v>6985143</v>
+        <v>6985152</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1642,7 +1652,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1720</t>
+          <t>2024_1716</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1652,7 +1662,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1662,7 +1672,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1682,7 +1692,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1693,10 +1703,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325254</v>
+        <v>123325252</v>
       </c>
       <c r="B10" t="n">
-        <v>56700</v>
+        <v>91277</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1705,25 +1715,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1731,16 +1741,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillingesbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611225</v>
+        <v>611224</v>
       </c>
       <c r="R10" t="n">
-        <v>6985116</v>
+        <v>6985137</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1767,7 +1782,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1706</t>
+          <t>2024_1708</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1777,7 +1792,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1787,12 +1802,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tupp</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1953,10 +1963,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325249</v>
+        <v>123325240</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>98100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1965,35 +1975,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2002,10 +2012,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611245</v>
+        <v>611190</v>
       </c>
       <c r="R12" t="n">
-        <v>6985142</v>
+        <v>6985143</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2032,7 +2042,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1711</t>
+          <t>2024_1720</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2042,7 +2052,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2052,7 +2062,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2083,10 +2093,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123325246</v>
+        <v>123325243</v>
       </c>
       <c r="B13" t="n">
-        <v>90990</v>
+        <v>56692</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2099,21 +2109,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2121,9 +2131,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2132,10 +2142,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611258</v>
+        <v>611249</v>
       </c>
       <c r="R13" t="n">
-        <v>6985139</v>
+        <v>6985155</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2162,7 +2172,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1714</t>
+          <t>2024_1717</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2172,7 +2182,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2182,7 +2192,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2213,10 +2223,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123325248</v>
+        <v>123325249</v>
       </c>
       <c r="B14" t="n">
-        <v>6271</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2225,35 +2235,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105336</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2262,10 +2272,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611232</v>
+        <v>611245</v>
       </c>
       <c r="R14" t="n">
-        <v>6985182</v>
+        <v>6985142</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2292,7 +2302,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1712</t>
+          <t>2024_1711</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2302,7 +2312,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2312,12 +2322,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Fragment</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2348,7 +2353,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123325241</v>
+        <v>123325246</v>
       </c>
       <c r="B15" t="n">
         <v>90990</v>
@@ -2383,12 +2388,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2397,10 +2402,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611259</v>
+        <v>611258</v>
       </c>
       <c r="R15" t="n">
-        <v>6985131</v>
+        <v>6985139</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2427,7 +2432,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1719</t>
+          <t>2024_1714</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2437,7 +2442,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2447,12 +2452,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>med eventuell ulltickeporing</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2483,7 +2483,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123325251</v>
+        <v>123325247</v>
       </c>
       <c r="B16" t="n">
         <v>90990</v>
@@ -2518,12 +2518,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611227</v>
+        <v>611257</v>
       </c>
       <c r="R16" t="n">
-        <v>6985131</v>
+        <v>6985139</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2024_1709</t>
+          <t>2024_1713</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
